--- a/tool/track-aggregator/master/地域共催-2025.xlsx
+++ b/tool/track-aggregator/master/地域共催-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B58BC40-5508-463D-A721-AA05636D8223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F95295-7837-40CD-9F56-1579A6C18F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
   <sheets>
     <sheet name="受講生一覧" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="620">
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
@@ -87,9 +87,6 @@
     <t>開発プロセス</t>
   </si>
   <si>
-    <t>Grp61-2026001</t>
-  </si>
-  <si>
     <t>Grp61-2026002</t>
   </si>
   <si>
@@ -960,19 +957,7 @@
     <t>L03</t>
   </si>
   <si>
-    <t>L01</t>
-  </si>
-  <si>
-    <t>L04</t>
-  </si>
-  <si>
-    <t>L02</t>
-  </si>
-  <si>
     <t>Grp68-2026008</t>
-  </si>
-  <si>
-    <t>青山 玲央</t>
   </si>
   <si>
     <t>伊賀 伶紗</t>
@@ -1949,6 +1934,21 @@
   </si>
   <si>
     <t>49080-645520</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>NTTデータサバイバル</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>社会を支えるITサービス2</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アルゴリズム入門2</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウモン</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -3009,7 +3009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7305DA-9532-48D5-A9AB-D0B7DDD41B28}">
-  <dimension ref="A1:G287"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="34.69921875" bestFit="1" customWidth="1"/>
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>4</v>
@@ -3045,23 +3045,23 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <f t="shared" ref="A2:A65" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A64" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>617</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -3073,19 +3073,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -3097,19 +3097,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -3121,19 +3121,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -3145,19 +3145,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -3169,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -3193,19 +3193,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -3217,19 +3217,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -3241,19 +3241,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -3265,19 +3265,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>316</v>
+        <v>596</v>
       </c>
       <c r="E11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -3289,19 +3289,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>601</v>
+        <v>312</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -3313,19 +3313,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -3337,19 +3337,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -3361,19 +3361,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E16" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -3409,19 +3409,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -3433,19 +3433,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C18" t="s">
         <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E18" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -3457,19 +3457,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
@@ -3481,19 +3481,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
@@ -3505,19 +3505,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C21" t="s">
         <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
@@ -3529,19 +3529,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
@@ -3553,19 +3553,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
@@ -3583,13 +3583,13 @@
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G24" t="b">
         <v>0</v>
@@ -3601,19 +3601,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C25" t="s">
         <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E25" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>
@@ -3625,19 +3625,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C26" t="s">
         <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E26" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
@@ -3649,19 +3649,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C27" t="s">
         <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E27" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C28" t="s">
         <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G28" t="b">
         <v>0</v>
@@ -3697,19 +3697,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C29" t="s">
         <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E29" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G29" t="b">
         <v>0</v>
@@ -3721,16 +3721,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E30" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>589</v>
@@ -3745,19 +3745,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C31" t="s">
         <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E31" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
@@ -3769,19 +3769,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C32" t="s">
         <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E32" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
@@ -3793,19 +3793,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C33" t="s">
         <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
@@ -3817,19 +3817,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C34" t="s">
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E34" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
@@ -3841,16 +3841,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C35" t="s">
         <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>589</v>
@@ -3865,19 +3865,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E36" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -3889,19 +3889,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C37" t="s">
         <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E37" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G37" t="b">
         <v>0</v>
@@ -3913,19 +3913,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C38" t="s">
         <v>48</v>
       </c>
       <c r="D38" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E38" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
@@ -3937,19 +3937,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C39" t="s">
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E39" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G39" t="b">
         <v>0</v>
@@ -3961,19 +3961,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C40" t="s">
         <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E40" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G40" t="b">
         <v>0</v>
@@ -3985,19 +3985,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C41" t="s">
         <v>51</v>
       </c>
       <c r="D41" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E41" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G41" t="b">
         <v>0</v>
@@ -4009,19 +4009,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C42" t="s">
         <v>52</v>
       </c>
       <c r="D42" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
@@ -4039,13 +4039,13 @@
         <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E43" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
@@ -4057,19 +4057,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C44" t="s">
         <v>54</v>
       </c>
       <c r="D44" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E44" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
@@ -4081,19 +4081,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C45" t="s">
         <v>55</v>
       </c>
       <c r="D45" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G45" t="b">
         <v>0</v>
@@ -4105,19 +4105,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C46" t="s">
         <v>56</v>
       </c>
       <c r="D46" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E46" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
@@ -4129,19 +4129,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C47" t="s">
         <v>57</v>
       </c>
       <c r="D47" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E47" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G47" t="b">
         <v>0</v>
@@ -4153,19 +4153,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C48" t="s">
         <v>58</v>
       </c>
       <c r="D48" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E48" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
@@ -4177,19 +4177,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C49" t="s">
         <v>59</v>
       </c>
       <c r="D49" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E49" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
@@ -4201,19 +4201,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C50" t="s">
         <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E50" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
@@ -4225,19 +4225,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C51" t="s">
         <v>61</v>
       </c>
       <c r="D51" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E51" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G51" t="b">
         <v>0</v>
@@ -4249,19 +4249,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C52" t="s">
         <v>62</v>
       </c>
       <c r="D52" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E52" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
@@ -4279,13 +4279,13 @@
         <v>63</v>
       </c>
       <c r="D53" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E53" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C54" t="s">
         <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E54" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
@@ -4321,19 +4321,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C55" t="s">
         <v>65</v>
       </c>
       <c r="D55" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E55" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
@@ -4345,19 +4345,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C56" t="s">
         <v>66</v>
       </c>
       <c r="D56" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E56" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
@@ -4369,19 +4369,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C57" t="s">
         <v>67</v>
       </c>
       <c r="D57" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E57" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G57" t="b">
         <v>0</v>
@@ -4393,19 +4393,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C58" t="s">
         <v>68</v>
       </c>
       <c r="D58" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E58" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
@@ -4417,19 +4417,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C59" t="s">
         <v>69</v>
       </c>
       <c r="D59" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E59" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G59" t="b">
         <v>0</v>
@@ -4441,19 +4441,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C60" t="s">
         <v>70</v>
       </c>
       <c r="D60" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E60" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
@@ -4465,19 +4465,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C61" t="s">
         <v>71</v>
       </c>
       <c r="D61" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E61" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G61" t="b">
         <v>0</v>
@@ -4489,19 +4489,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C62" t="s">
         <v>72</v>
       </c>
       <c r="D62" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E62" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
@@ -4513,19 +4513,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E63" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
@@ -4537,19 +4537,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C64" t="s">
         <v>74</v>
       </c>
       <c r="D64" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E64" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G64" t="b">
         <v>0</v>
@@ -4557,23 +4557,23 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A65:A128" si="1">ROW()-1</f>
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C65" t="s">
         <v>75</v>
       </c>
       <c r="D65" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E65" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G65" t="b">
         <v>0</v>
@@ -4581,23 +4581,23 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
-        <f t="shared" ref="A66:A129" si="1">ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C66" t="s">
         <v>76</v>
       </c>
       <c r="D66" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E66" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
@@ -4609,19 +4609,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C67" t="s">
         <v>77</v>
       </c>
       <c r="D67" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E67" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
@@ -4633,19 +4633,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" t="s">
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E68" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>79</v>
       </c>
       <c r="D69" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E69" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G69" t="b">
         <v>0</v>
@@ -4681,19 +4681,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C70" t="s">
         <v>80</v>
       </c>
       <c r="D70" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E70" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G70" t="b">
         <v>0</v>
@@ -4705,19 +4705,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C71" t="s">
         <v>81</v>
       </c>
       <c r="D71" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E71" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G71" t="b">
         <v>0</v>
@@ -4729,19 +4729,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" t="s">
         <v>82</v>
       </c>
       <c r="D72" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E72" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
@@ -4753,19 +4753,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C73" t="s">
         <v>83</v>
       </c>
       <c r="D73" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E73" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
@@ -4777,19 +4777,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C74" t="s">
         <v>84</v>
       </c>
       <c r="D74" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E74" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G74" t="b">
         <v>0</v>
@@ -4801,19 +4801,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C75" t="s">
         <v>85</v>
       </c>
       <c r="D75" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E75" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G75" t="b">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C76" t="s">
         <v>86</v>
       </c>
       <c r="D76" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E76" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="G76" t="b">
         <v>0</v>
@@ -4849,19 +4849,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C77" t="s">
         <v>87</v>
       </c>
       <c r="D77" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E77" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G77" t="b">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C78" t="s">
         <v>88</v>
       </c>
       <c r="D78" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E78" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G78" t="b">
         <v>0</v>
@@ -4897,19 +4897,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C79" t="s">
         <v>89</v>
       </c>
       <c r="D79" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E79" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G79" t="b">
         <v>0</v>
@@ -4921,19 +4921,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C80" t="s">
         <v>90</v>
       </c>
       <c r="D80" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E80" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G80" t="b">
         <v>0</v>
@@ -4945,19 +4945,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C81" t="s">
         <v>91</v>
       </c>
       <c r="D81" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E81" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G81" t="b">
         <v>0</v>
@@ -4969,19 +4969,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C82" t="s">
         <v>92</v>
       </c>
       <c r="D82" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E82" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G82" t="b">
         <v>0</v>
@@ -4993,19 +4993,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C83" t="s">
         <v>93</v>
       </c>
       <c r="D83" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E83" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G83" t="b">
         <v>0</v>
@@ -5017,19 +5017,19 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C84" t="s">
         <v>94</v>
       </c>
       <c r="D84" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E84" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="G84" t="b">
         <v>0</v>
@@ -5041,19 +5041,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C85" t="s">
         <v>95</v>
       </c>
       <c r="D85" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E85" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G85" t="b">
         <v>0</v>
@@ -5065,19 +5065,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C86" t="s">
         <v>96</v>
       </c>
       <c r="D86" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E86" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G86" t="b">
         <v>0</v>
@@ -5089,19 +5089,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" t="s">
         <v>97</v>
       </c>
       <c r="D87" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E87" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G87" t="b">
         <v>0</v>
@@ -5113,19 +5113,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C88" t="s">
         <v>98</v>
       </c>
       <c r="D88" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E88" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G88" t="b">
         <v>0</v>
@@ -5137,19 +5137,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C89" t="s">
         <v>99</v>
       </c>
       <c r="D89" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E89" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G89" t="b">
         <v>0</v>
@@ -5161,19 +5161,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C90" t="s">
         <v>100</v>
       </c>
       <c r="D90" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E90" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
@@ -5185,19 +5185,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C91" t="s">
         <v>101</v>
       </c>
       <c r="D91" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E91" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G91" t="b">
         <v>0</v>
@@ -5209,16 +5209,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C92" t="s">
         <v>102</v>
       </c>
       <c r="D92" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E92" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>589</v>
@@ -5233,19 +5233,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C93" t="s">
         <v>103</v>
       </c>
       <c r="D93" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E93" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="G93" t="b">
         <v>0</v>
@@ -5257,19 +5257,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C94" t="s">
         <v>104</v>
       </c>
       <c r="D94" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E94" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="G94" t="b">
         <v>0</v>
@@ -5281,19 +5281,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C95" t="s">
         <v>105</v>
       </c>
       <c r="D95" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E95" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="G95" t="b">
         <v>0</v>
@@ -5305,19 +5305,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C96" t="s">
         <v>106</v>
       </c>
       <c r="D96" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E96" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G96" t="b">
         <v>0</v>
@@ -5329,19 +5329,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C97" t="s">
         <v>107</v>
       </c>
       <c r="D97" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E97" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G97" t="b">
         <v>0</v>
@@ -5353,19 +5353,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C98" t="s">
         <v>108</v>
       </c>
       <c r="D98" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E98" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G98" t="b">
         <v>0</v>
@@ -5377,19 +5377,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C99" t="s">
         <v>109</v>
       </c>
       <c r="D99" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E99" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="G99" t="b">
         <v>0</v>
@@ -5401,19 +5401,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C100" t="s">
         <v>110</v>
       </c>
       <c r="D100" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G100" t="b">
         <v>0</v>
@@ -5425,19 +5425,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C101" t="s">
         <v>111</v>
       </c>
       <c r="D101" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E101" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="G101" t="b">
         <v>0</v>
@@ -5449,19 +5449,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C102" t="s">
         <v>112</v>
       </c>
       <c r="D102" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E102" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G102" t="b">
         <v>0</v>
@@ -5473,19 +5473,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C103" t="s">
         <v>113</v>
       </c>
       <c r="D103" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E103" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G103" t="b">
         <v>0</v>
@@ -5497,19 +5497,19 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C104" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E104" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G104" t="b">
         <v>0</v>
@@ -5521,19 +5521,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C105" t="s">
         <v>115</v>
       </c>
       <c r="D105" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E105" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G105" t="b">
         <v>0</v>
@@ -5545,19 +5545,19 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C106" t="s">
         <v>116</v>
       </c>
       <c r="D106" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E106" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="G106" t="b">
         <v>0</v>
@@ -5569,19 +5569,19 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C107" t="s">
         <v>117</v>
       </c>
       <c r="D107" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E107" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G107" t="b">
         <v>0</v>
@@ -5593,19 +5593,19 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C108" t="s">
         <v>118</v>
       </c>
       <c r="D108" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E108" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G108" t="b">
         <v>0</v>
@@ -5617,19 +5617,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C109" t="s">
         <v>119</v>
       </c>
       <c r="D109" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E109" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G109" t="b">
         <v>0</v>
@@ -5641,19 +5641,19 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C110" t="s">
         <v>120</v>
       </c>
       <c r="D110" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E110" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G110" t="b">
         <v>0</v>
@@ -5665,19 +5665,19 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C111" t="s">
         <v>121</v>
       </c>
       <c r="D111" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E111" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G111" t="b">
         <v>0</v>
@@ -5689,19 +5689,19 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C112" t="s">
         <v>122</v>
       </c>
       <c r="D112" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E112" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G112" t="b">
         <v>0</v>
@@ -5713,19 +5713,19 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C113" t="s">
         <v>123</v>
       </c>
       <c r="D113" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E113" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="G113" t="b">
         <v>0</v>
@@ -5737,19 +5737,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C114" t="s">
         <v>124</v>
       </c>
       <c r="D114" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E114" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G114" t="b">
         <v>0</v>
@@ -5761,19 +5761,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C115" t="s">
         <v>125</v>
       </c>
       <c r="D115" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E115" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G115" t="b">
         <v>0</v>
@@ -5785,19 +5785,19 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C116" t="s">
         <v>126</v>
       </c>
       <c r="D116" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E116" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G116" t="b">
         <v>0</v>
@@ -5809,19 +5809,19 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C117" t="s">
         <v>127</v>
       </c>
       <c r="D117" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E117" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G117" t="b">
         <v>0</v>
@@ -5833,19 +5833,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C118" t="s">
         <v>128</v>
       </c>
       <c r="D118" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E118" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G118" t="b">
         <v>0</v>
@@ -5857,19 +5857,19 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C119" t="s">
         <v>129</v>
       </c>
       <c r="D119" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E119" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G119" t="b">
         <v>0</v>
@@ -5881,19 +5881,19 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C120" t="s">
         <v>130</v>
       </c>
       <c r="D120" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E120" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G120" t="b">
         <v>0</v>
@@ -5905,19 +5905,19 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C121" t="s">
         <v>131</v>
       </c>
       <c r="D121" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E121" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G121" t="b">
         <v>0</v>
@@ -5929,19 +5929,19 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C122" t="s">
         <v>132</v>
       </c>
       <c r="D122" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E122" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G122" t="b">
         <v>0</v>
@@ -5953,19 +5953,19 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C123" t="s">
         <v>133</v>
       </c>
       <c r="D123" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E123" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G123" t="b">
         <v>0</v>
@@ -5977,19 +5977,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C124" t="s">
         <v>134</v>
       </c>
       <c r="D124" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E124" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G124" t="b">
         <v>0</v>
@@ -6007,13 +6007,13 @@
         <v>135</v>
       </c>
       <c r="D125" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E125" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G125" t="b">
         <v>0</v>
@@ -6025,19 +6025,19 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C126" t="s">
         <v>136</v>
       </c>
       <c r="D126" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E126" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G126" t="b">
         <v>0</v>
@@ -6049,19 +6049,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C127" t="s">
         <v>137</v>
       </c>
       <c r="D127" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E127" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G127" t="b">
         <v>0</v>
@@ -6073,19 +6073,19 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C128" t="s">
         <v>138</v>
       </c>
       <c r="D128" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E128" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="G128" t="b">
         <v>0</v>
@@ -6093,23 +6093,23 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A129:A192" si="2">ROW()-1</f>
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C129" t="s">
         <v>139</v>
       </c>
       <c r="D129" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E129" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="G129" t="b">
         <v>0</v>
@@ -6117,23 +6117,23 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
-        <f t="shared" ref="A130:A193" si="2">ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C130" t="s">
         <v>140</v>
       </c>
       <c r="D130" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E130" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G130" t="b">
         <v>0</v>
@@ -6145,19 +6145,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C131" t="s">
         <v>141</v>
       </c>
       <c r="D131" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="E131" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G131" t="b">
         <v>0</v>
@@ -6169,19 +6169,19 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C132" t="s">
         <v>142</v>
       </c>
       <c r="D132" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E132" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G132" t="b">
         <v>0</v>
@@ -6193,19 +6193,19 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C133" t="s">
         <v>143</v>
       </c>
       <c r="D133" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E133" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G133" t="b">
         <v>0</v>
@@ -6217,16 +6217,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C134" t="s">
         <v>144</v>
       </c>
       <c r="D134" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E134" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>589</v>
@@ -6241,19 +6241,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C135" t="s">
         <v>145</v>
       </c>
       <c r="D135" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E135" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G135" t="b">
         <v>0</v>
@@ -6265,19 +6265,19 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C136" t="s">
         <v>146</v>
       </c>
       <c r="D136" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E136" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G136" t="b">
         <v>0</v>
@@ -6289,19 +6289,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C137" t="s">
         <v>147</v>
       </c>
       <c r="D137" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E137" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G137" t="b">
         <v>0</v>
@@ -6313,19 +6313,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C138" t="s">
         <v>148</v>
       </c>
       <c r="D138" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E138" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G138" t="b">
         <v>0</v>
@@ -6337,19 +6337,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C139" t="s">
         <v>149</v>
       </c>
       <c r="D139" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E139" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G139" t="b">
         <v>0</v>
@@ -6361,19 +6361,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C140" t="s">
         <v>150</v>
       </c>
       <c r="D140" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E140" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G140" t="b">
         <v>0</v>
@@ -6385,19 +6385,19 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C141" t="s">
         <v>151</v>
       </c>
       <c r="D141" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E141" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G141" t="b">
         <v>0</v>
@@ -6409,19 +6409,19 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C142" t="s">
         <v>152</v>
       </c>
       <c r="D142" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E142" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G142" t="b">
         <v>0</v>
@@ -6433,19 +6433,19 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C143" t="s">
         <v>153</v>
       </c>
       <c r="D143" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E143" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G143" t="b">
         <v>0</v>
@@ -6457,19 +6457,19 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C144" t="s">
         <v>154</v>
       </c>
       <c r="D144" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E144" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G144" t="b">
         <v>0</v>
@@ -6481,19 +6481,19 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C145" t="s">
         <v>155</v>
       </c>
       <c r="D145" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E145" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G145" t="b">
         <v>0</v>
@@ -6505,19 +6505,19 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C146" t="s">
         <v>156</v>
       </c>
       <c r="D146" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E146" t="s">
-        <v>303</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>591</v>
+        <v>301</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>584</v>
       </c>
       <c r="G146" t="b">
         <v>0</v>
@@ -6529,19 +6529,19 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C147" t="s">
         <v>157</v>
       </c>
       <c r="D147" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E147" t="s">
-        <v>304</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>589</v>
+        <v>301</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="G147" t="b">
         <v>0</v>
@@ -6553,19 +6553,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C148" t="s">
         <v>158</v>
       </c>
       <c r="D148" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E148" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G148" t="b">
         <v>0</v>
@@ -6577,19 +6577,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C149" t="s">
         <v>159</v>
       </c>
       <c r="D149" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E149" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G149" t="b">
         <v>0</v>
@@ -6601,19 +6601,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C150" t="s">
         <v>160</v>
       </c>
       <c r="D150" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E150" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G150" t="b">
         <v>0</v>
@@ -6625,19 +6625,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C151" t="s">
         <v>161</v>
       </c>
       <c r="D151" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E151" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="G151" t="b">
         <v>0</v>
@@ -6649,19 +6649,19 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C152" t="s">
         <v>162</v>
       </c>
       <c r="D152" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E152" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="G152" t="b">
         <v>0</v>
@@ -6673,19 +6673,19 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C153" t="s">
         <v>163</v>
       </c>
       <c r="D153" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E153" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G153" t="b">
         <v>0</v>
@@ -6697,19 +6697,19 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C154" t="s">
         <v>164</v>
       </c>
       <c r="D154" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E154" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G154" t="b">
         <v>0</v>
@@ -6721,19 +6721,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C155" t="s">
         <v>165</v>
       </c>
       <c r="D155" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E155" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G155" t="b">
         <v>0</v>
@@ -6745,19 +6745,19 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C156" t="s">
         <v>166</v>
       </c>
       <c r="D156" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E156" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G156" t="b">
         <v>0</v>
@@ -6769,19 +6769,19 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C157" t="s">
         <v>167</v>
       </c>
       <c r="D157" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E157" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G157" t="b">
         <v>0</v>
@@ -6793,19 +6793,19 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C158" t="s">
         <v>168</v>
       </c>
       <c r="D158" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E158" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G158" t="b">
         <v>0</v>
@@ -6817,19 +6817,19 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C159" t="s">
         <v>169</v>
       </c>
       <c r="D159" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E159" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G159" t="b">
         <v>0</v>
@@ -6841,19 +6841,19 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C160" t="s">
         <v>170</v>
       </c>
       <c r="D160" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E160" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G160" t="b">
         <v>0</v>
@@ -6865,19 +6865,19 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C161" t="s">
         <v>171</v>
       </c>
       <c r="D161" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E161" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G161" t="b">
         <v>0</v>
@@ -6889,19 +6889,19 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C162" t="s">
         <v>172</v>
       </c>
       <c r="D162" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E162" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G162" t="b">
         <v>0</v>
@@ -6913,19 +6913,19 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C163" t="s">
         <v>173</v>
       </c>
       <c r="D163" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E163" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G163" t="b">
         <v>0</v>
@@ -6937,19 +6937,19 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C164" t="s">
         <v>174</v>
       </c>
       <c r="D164" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E164" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G164" t="b">
         <v>0</v>
@@ -6961,19 +6961,19 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C165" t="s">
         <v>175</v>
       </c>
       <c r="D165" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E165" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G165" t="b">
         <v>0</v>
@@ -6985,19 +6985,19 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C166" t="s">
         <v>176</v>
       </c>
       <c r="D166" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E166" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G166" t="b">
         <v>0</v>
@@ -7009,19 +7009,19 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C167" t="s">
         <v>177</v>
       </c>
       <c r="D167" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E167" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G167" t="b">
         <v>0</v>
@@ -7033,19 +7033,19 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C168" t="s">
         <v>178</v>
       </c>
       <c r="D168" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E168" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G168" t="b">
         <v>0</v>
@@ -7057,19 +7057,19 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C169" t="s">
         <v>179</v>
       </c>
       <c r="D169" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E169" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G169" t="b">
         <v>0</v>
@@ -7081,19 +7081,19 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C170" t="s">
         <v>180</v>
       </c>
       <c r="D170" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E170" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G170" t="b">
         <v>0</v>
@@ -7105,19 +7105,19 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C171" t="s">
         <v>181</v>
       </c>
       <c r="D171" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E171" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G171" t="b">
         <v>0</v>
@@ -7129,19 +7129,19 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C172" t="s">
         <v>182</v>
       </c>
       <c r="D172" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E172" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G172" t="b">
         <v>0</v>
@@ -7153,19 +7153,19 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C173" t="s">
         <v>183</v>
       </c>
       <c r="D173" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E173" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G173" t="b">
         <v>0</v>
@@ -7177,19 +7177,19 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C174" t="s">
         <v>184</v>
       </c>
       <c r="D174" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E174" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G174" t="b">
         <v>0</v>
@@ -7201,19 +7201,19 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C175" t="s">
         <v>185</v>
       </c>
       <c r="D175" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E175" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G175" t="b">
         <v>0</v>
@@ -7225,19 +7225,19 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C176" t="s">
         <v>186</v>
       </c>
       <c r="D176" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E176" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G176" t="b">
         <v>0</v>
@@ -7249,19 +7249,19 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C177" t="s">
         <v>187</v>
       </c>
       <c r="D177" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E177" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G177" t="b">
         <v>0</v>
@@ -7273,19 +7273,19 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C178" t="s">
         <v>188</v>
       </c>
       <c r="D178" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E178" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G178" t="b">
         <v>0</v>
@@ -7297,19 +7297,19 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C179" t="s">
         <v>189</v>
       </c>
       <c r="D179" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E179" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="G179" t="b">
         <v>0</v>
@@ -7321,19 +7321,19 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C180" t="s">
         <v>190</v>
       </c>
       <c r="D180" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E180" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G180" t="b">
         <v>0</v>
@@ -7345,19 +7345,19 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C181" t="s">
         <v>191</v>
       </c>
       <c r="D181" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E181" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G181" t="b">
         <v>0</v>
@@ -7369,19 +7369,19 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C182" t="s">
         <v>192</v>
       </c>
       <c r="D182" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E182" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G182" t="b">
         <v>0</v>
@@ -7393,19 +7393,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C183" t="s">
         <v>193</v>
       </c>
       <c r="D183" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E183" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G183" t="b">
         <v>0</v>
@@ -7417,19 +7417,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C184" t="s">
         <v>194</v>
       </c>
       <c r="D184" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E184" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G184" t="b">
         <v>0</v>
@@ -7441,19 +7441,19 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C185" t="s">
         <v>195</v>
       </c>
       <c r="D185" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E185" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="G185" t="b">
         <v>0</v>
@@ -7465,19 +7465,19 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C186" t="s">
         <v>196</v>
       </c>
       <c r="D186" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E186" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G186" t="b">
         <v>0</v>
@@ -7489,19 +7489,19 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C187" t="s">
         <v>197</v>
       </c>
       <c r="D187" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E187" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G187" t="b">
         <v>0</v>
@@ -7513,19 +7513,19 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C188" t="s">
         <v>198</v>
       </c>
       <c r="D188" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E188" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G188" t="b">
         <v>0</v>
@@ -7537,19 +7537,19 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C189" t="s">
         <v>199</v>
       </c>
       <c r="D189" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="E189" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G189" t="b">
         <v>0</v>
@@ -7561,19 +7561,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C190" t="s">
         <v>200</v>
       </c>
       <c r="D190" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E190" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="G190" t="b">
         <v>0</v>
@@ -7585,19 +7585,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C191" t="s">
         <v>201</v>
       </c>
       <c r="D191" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E191" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G191" t="b">
         <v>0</v>
@@ -7609,16 +7609,16 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C192" t="s">
         <v>202</v>
       </c>
       <c r="D192" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E192" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>589</v>
@@ -7629,23 +7629,23 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A193:A256" si="3">ROW()-1</f>
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C193" t="s">
         <v>203</v>
       </c>
       <c r="D193" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E193" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="G193" t="b">
         <v>0</v>
@@ -7653,23 +7653,23 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194">
-        <f t="shared" ref="A194:A257" si="3">ROW()-1</f>
+        <f t="shared" si="3"/>
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C194" t="s">
         <v>204</v>
       </c>
       <c r="D194" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E194" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G194" t="b">
         <v>0</v>
@@ -7681,19 +7681,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C195" t="s">
         <v>205</v>
       </c>
       <c r="D195" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E195" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G195" t="b">
         <v>0</v>
@@ -7705,19 +7705,19 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C196" t="s">
         <v>206</v>
       </c>
       <c r="D196" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E196" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G196" t="b">
         <v>0</v>
@@ -7729,19 +7729,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C197" t="s">
         <v>207</v>
       </c>
       <c r="D197" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E197" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G197" t="b">
         <v>0</v>
@@ -7753,19 +7753,19 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C198" t="s">
         <v>208</v>
       </c>
       <c r="D198" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E198" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G198" t="b">
         <v>0</v>
@@ -7777,19 +7777,19 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C199" t="s">
         <v>209</v>
       </c>
       <c r="D199" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E199" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G199" t="b">
         <v>0</v>
@@ -7801,19 +7801,19 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C200" t="s">
         <v>210</v>
       </c>
       <c r="D200" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E200" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G200" t="b">
         <v>0</v>
@@ -7825,19 +7825,19 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C201" t="s">
         <v>211</v>
       </c>
       <c r="D201" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="E201" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G201" t="b">
         <v>0</v>
@@ -7849,19 +7849,19 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C202" t="s">
         <v>212</v>
       </c>
       <c r="D202" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E202" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G202" t="b">
         <v>0</v>
@@ -7873,19 +7873,19 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C203" t="s">
         <v>213</v>
       </c>
       <c r="D203" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E203" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G203" t="b">
         <v>0</v>
@@ -7903,13 +7903,13 @@
         <v>214</v>
       </c>
       <c r="D204" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="E204" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G204" t="b">
         <v>0</v>
@@ -7921,19 +7921,19 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C205" t="s">
         <v>215</v>
       </c>
       <c r="D205" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E205" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G205" t="b">
         <v>0</v>
@@ -7945,19 +7945,19 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C206" t="s">
         <v>216</v>
       </c>
       <c r="D206" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E206" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G206" t="b">
         <v>0</v>
@@ -7969,19 +7969,19 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C207" t="s">
         <v>217</v>
       </c>
       <c r="D207" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E207" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G207" t="b">
         <v>0</v>
@@ -7993,19 +7993,19 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C208" t="s">
         <v>218</v>
       </c>
       <c r="D208" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E208" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G208" t="b">
         <v>0</v>
@@ -8017,19 +8017,19 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C209" t="s">
         <v>219</v>
       </c>
       <c r="D209" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E209" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="G209" t="b">
         <v>0</v>
@@ -8041,19 +8041,19 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C210" t="s">
         <v>220</v>
       </c>
       <c r="D210" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E210" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G210" t="b">
         <v>0</v>
@@ -8065,19 +8065,19 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C211" t="s">
         <v>221</v>
       </c>
       <c r="D211" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E211" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G211" t="b">
         <v>0</v>
@@ -8089,19 +8089,19 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C212" t="s">
         <v>222</v>
       </c>
       <c r="D212" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E212" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G212" t="b">
         <v>0</v>
@@ -8113,19 +8113,19 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C213" t="s">
         <v>223</v>
       </c>
       <c r="D213" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E213" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G213" t="b">
         <v>0</v>
@@ -8143,13 +8143,13 @@
         <v>224</v>
       </c>
       <c r="D214" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="G214" t="b">
         <v>0</v>
@@ -8161,19 +8161,19 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C215" t="s">
         <v>225</v>
       </c>
       <c r="D215" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E215" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G215" t="b">
         <v>0</v>
@@ -8185,19 +8185,19 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C216" t="s">
         <v>226</v>
       </c>
       <c r="D216" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E216" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="G216" t="b">
         <v>0</v>
@@ -8209,19 +8209,19 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C217" t="s">
         <v>227</v>
       </c>
       <c r="D217" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E217" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G217" t="b">
         <v>0</v>
@@ -8233,19 +8233,19 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C218" t="s">
         <v>228</v>
       </c>
       <c r="D218" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E218" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G218" t="b">
         <v>0</v>
@@ -8257,19 +8257,19 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C219" t="s">
         <v>229</v>
       </c>
       <c r="D219" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G219" t="b">
         <v>0</v>
@@ -8281,19 +8281,19 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C220" t="s">
         <v>230</v>
       </c>
       <c r="D220" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G220" t="b">
         <v>0</v>
@@ -8305,22 +8305,22 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C221" t="s">
-        <v>231</v>
+        <v>302</v>
       </c>
       <c r="D221" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E221" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -8329,22 +8329,22 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C222" t="s">
-        <v>306</v>
+        <v>231</v>
       </c>
       <c r="D222" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E222" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F222" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -8353,19 +8353,19 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C223" t="s">
         <v>232</v>
       </c>
       <c r="D223" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E223" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F223" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G223" t="b">
         <v>0</v>
@@ -8377,19 +8377,19 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C224" t="s">
         <v>233</v>
       </c>
       <c r="D224" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E224" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G224" t="b">
         <v>0</v>
@@ -8401,19 +8401,19 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C225" t="s">
         <v>234</v>
       </c>
       <c r="D225" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E225" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G225" t="b">
         <v>0</v>
@@ -8425,19 +8425,19 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C226" t="s">
         <v>235</v>
       </c>
       <c r="D226" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E226" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F226" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G226" t="b">
         <v>0</v>
@@ -8449,19 +8449,19 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C227" t="s">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="D227" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E227" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G227" t="b">
         <v>0</v>
@@ -8476,16 +8476,16 @@
         <v>298</v>
       </c>
       <c r="C228" t="s">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="D228" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E228" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="G228" t="b">
         <v>0</v>
@@ -8497,19 +8497,19 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C229" t="s">
         <v>237</v>
       </c>
       <c r="D229" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E229" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G229" t="b">
         <v>0</v>
@@ -8521,19 +8521,19 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C230" t="s">
         <v>238</v>
       </c>
       <c r="D230" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E230" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="G230" t="b">
         <v>0</v>
@@ -8545,19 +8545,19 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C231" t="s">
         <v>239</v>
       </c>
       <c r="D231" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E231" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G231" t="b">
         <v>0</v>
@@ -8569,19 +8569,19 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C232" t="s">
         <v>240</v>
       </c>
       <c r="D232" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E232" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F232" s="6" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G232" t="b">
         <v>0</v>
@@ -8593,19 +8593,19 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C233" t="s">
         <v>241</v>
       </c>
       <c r="D233" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E233" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G233" t="b">
         <v>0</v>
@@ -8617,19 +8617,19 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C234" t="s">
         <v>242</v>
       </c>
       <c r="D234" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E234" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F234" s="6" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="G234" t="b">
         <v>0</v>
@@ -8641,19 +8641,19 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C235" t="s">
         <v>243</v>
       </c>
       <c r="D235" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E235" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F235" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G235" t="b">
         <v>0</v>
@@ -8665,19 +8665,19 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C236" t="s">
         <v>244</v>
       </c>
       <c r="D236" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E236" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G236" t="b">
         <v>0</v>
@@ -8689,19 +8689,19 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C237" t="s">
         <v>245</v>
       </c>
       <c r="D237" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E237" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F237" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G237" t="b">
         <v>0</v>
@@ -8713,19 +8713,19 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C238" t="s">
         <v>246</v>
       </c>
       <c r="D238" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E238" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F238" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G238" t="b">
         <v>0</v>
@@ -8737,19 +8737,19 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C239" t="s">
         <v>247</v>
       </c>
       <c r="D239" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E239" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F239" s="6" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G239" t="b">
         <v>0</v>
@@ -8761,19 +8761,19 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C240" t="s">
         <v>248</v>
       </c>
       <c r="D240" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E240" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F240" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G240" t="b">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C241" t="s">
         <v>249</v>
       </c>
       <c r="D241" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E241" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G241" t="b">
         <v>0</v>
@@ -8809,19 +8809,19 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C242" t="s">
         <v>250</v>
       </c>
       <c r="D242" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E242" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F242" s="6" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G242" t="b">
         <v>0</v>
@@ -8833,19 +8833,19 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C243" t="s">
         <v>251</v>
       </c>
       <c r="D243" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E243" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F243" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G243" t="b">
         <v>0</v>
@@ -8857,19 +8857,19 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C244" t="s">
         <v>252</v>
       </c>
       <c r="D244" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E244" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F244" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G244" t="b">
         <v>0</v>
@@ -8881,16 +8881,16 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C245" t="s">
         <v>253</v>
       </c>
       <c r="D245" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E245" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F245" s="6" t="s">
         <v>589</v>
@@ -8905,19 +8905,19 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C246" t="s">
         <v>254</v>
       </c>
       <c r="D246" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E246" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F246" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="G246" t="b">
         <v>0</v>
@@ -8929,19 +8929,19 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C247" t="s">
         <v>255</v>
       </c>
       <c r="D247" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="E247" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G247" t="b">
         <v>0</v>
@@ -8953,19 +8953,19 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C248" t="s">
         <v>256</v>
       </c>
       <c r="D248" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E248" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F248" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G248" t="b">
         <v>0</v>
@@ -8977,19 +8977,19 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C249" t="s">
         <v>257</v>
       </c>
       <c r="D249" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E249" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F249" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G249" t="b">
         <v>0</v>
@@ -9001,19 +9001,19 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C250" t="s">
         <v>258</v>
       </c>
       <c r="D250" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E250" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F250" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G250" t="b">
         <v>0</v>
@@ -9025,19 +9025,19 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C251" t="s">
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E251" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F251" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G251" t="b">
         <v>0</v>
@@ -9049,16 +9049,16 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C252" t="s">
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="E252" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F252" s="6" t="s">
         <v>589</v>
@@ -9073,19 +9073,19 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C253" t="s">
         <v>261</v>
       </c>
       <c r="D253" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E253" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F253" s="6" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="G253" t="b">
         <v>0</v>
@@ -9097,19 +9097,19 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C254" t="s">
         <v>262</v>
       </c>
       <c r="D254" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E254" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F254" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G254" t="b">
         <v>0</v>
@@ -9121,19 +9121,19 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C255" t="s">
         <v>263</v>
       </c>
       <c r="D255" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E255" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F255" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G255" t="b">
         <v>0</v>
@@ -9145,19 +9145,19 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C256" t="s">
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E256" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F256" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G256" t="b">
         <v>0</v>
@@ -9165,23 +9165,23 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A257:A280" si="4">ROW()-1</f>
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C257" t="s">
         <v>265</v>
       </c>
       <c r="D257" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E257" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F257" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G257" t="b">
         <v>0</v>
@@ -9189,23 +9189,23 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258">
-        <f t="shared" ref="A258:A281" si="4">ROW()-1</f>
+        <f t="shared" si="4"/>
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C258" t="s">
         <v>266</v>
       </c>
       <c r="D258" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E258" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F258" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G258" t="b">
         <v>0</v>
@@ -9217,19 +9217,19 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C259" t="s">
         <v>267</v>
       </c>
       <c r="D259" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="E259" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F259" s="6" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G259" t="b">
         <v>0</v>
@@ -9241,19 +9241,19 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C260" t="s">
         <v>268</v>
       </c>
       <c r="D260" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="E260" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F260" s="6" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="G260" t="b">
         <v>0</v>
@@ -9271,13 +9271,13 @@
         <v>269</v>
       </c>
       <c r="D261" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="E261" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F261" s="6" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G261" t="b">
         <v>0</v>
@@ -9289,19 +9289,19 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C262" t="s">
         <v>270</v>
       </c>
       <c r="D262" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E262" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F262" s="6" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G262" t="b">
         <v>0</v>
@@ -9313,19 +9313,19 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C263" t="s">
         <v>271</v>
       </c>
       <c r="D263" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E263" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F263" s="6" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G263" t="b">
         <v>0</v>
@@ -9337,19 +9337,19 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C264" t="s">
         <v>272</v>
       </c>
       <c r="D264" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="E264" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F264" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G264" t="b">
         <v>0</v>
@@ -9361,19 +9361,19 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C265" t="s">
         <v>273</v>
       </c>
       <c r="D265" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E265" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F265" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G265" t="b">
         <v>0</v>
@@ -9385,19 +9385,19 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C266" t="s">
         <v>274</v>
       </c>
       <c r="D266" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E266" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F266" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G266" t="b">
         <v>0</v>
@@ -9409,19 +9409,19 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C267" t="s">
         <v>275</v>
       </c>
       <c r="D267" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E267" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G267" t="b">
         <v>0</v>
@@ -9433,19 +9433,19 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C268" t="s">
         <v>276</v>
       </c>
       <c r="D268" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E268" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F268" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G268" t="b">
         <v>0</v>
@@ -9457,19 +9457,19 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C269" t="s">
         <v>277</v>
       </c>
       <c r="D269" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E269" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F269" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G269" t="b">
         <v>0</v>
@@ -9481,19 +9481,19 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C270" t="s">
         <v>278</v>
       </c>
       <c r="D270" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E270" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F270" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G270" t="b">
         <v>0</v>
@@ -9505,19 +9505,19 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C271" t="s">
         <v>279</v>
       </c>
       <c r="D271" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E271" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F271" s="6" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="G271" t="b">
         <v>0</v>
@@ -9529,19 +9529,19 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C272" t="s">
         <v>280</v>
       </c>
       <c r="D272" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E272" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F272" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G272" t="b">
         <v>0</v>
@@ -9559,13 +9559,13 @@
         <v>281</v>
       </c>
       <c r="D273" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E273" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G273" t="b">
         <v>0</v>
@@ -9577,19 +9577,19 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C274" t="s">
         <v>282</v>
       </c>
       <c r="D274" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E274" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F274" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G274" t="b">
         <v>0</v>
@@ -9601,19 +9601,19 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C275" t="s">
         <v>283</v>
       </c>
       <c r="D275" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E275" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F275" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G275" t="b">
         <v>0</v>
@@ -9625,19 +9625,19 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C276" t="s">
         <v>284</v>
       </c>
       <c r="D276" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E276" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F276" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G276" t="b">
         <v>0</v>
@@ -9649,19 +9649,19 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C277" t="s">
         <v>285</v>
       </c>
       <c r="D277" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E277" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F277" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G277" t="b">
         <v>0</v>
@@ -9673,43 +9673,43 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C278" t="s">
         <v>286</v>
       </c>
       <c r="D278" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E278" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F278" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G278" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A279">
         <f t="shared" si="4"/>
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C279" t="s">
         <v>287</v>
       </c>
       <c r="D279" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="E279" t="s">
-        <v>304</v>
-      </c>
-      <c r="F279" s="6" t="s">
-        <v>593</v>
+        <v>301</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="G279" t="b">
         <v>0</v>
@@ -9721,47 +9721,26 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C280" t="s">
         <v>288</v>
       </c>
       <c r="D280" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E280" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G280" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A281">
-        <f t="shared" si="4"/>
-        <v>280</v>
-      </c>
-      <c r="B281" t="s">
-        <v>301</v>
-      </c>
-      <c r="C281" t="s">
-        <v>289</v>
-      </c>
-      <c r="D281" t="s">
-        <v>585</v>
-      </c>
-      <c r="E281" t="s">
-        <v>304</v>
-      </c>
-      <c r="F281" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="G281" t="b">
-        <v>0</v>
-      </c>
+      <c r="F281" s="3"/>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F282" s="3"/>
@@ -9777,9 +9756,6 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F286" s="3"/>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="F287" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
@@ -9802,13 +9778,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
@@ -9820,10 +9796,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>586</v>
+        <v>618</v>
       </c>
       <c r="C2" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -9838,10 +9814,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C3" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -9859,7 +9835,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -9877,7 +9853,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -9895,7 +9871,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -9913,7 +9889,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -9931,7 +9907,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -9949,7 +9925,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -9978,13 +9954,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>600</v>
-      </c>
       <c r="D1" s="8" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
@@ -9996,10 +9972,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C2" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -10014,10 +9990,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="C3" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -10035,7 +10011,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -10053,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -10071,7 +10047,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -10089,7 +10065,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -10107,7 +10083,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -10125,7 +10101,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -10140,10 +10116,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C10" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -10158,10 +10134,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C11" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -10176,10 +10152,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C12" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
